--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T08:58:38+00:00</t>
+    <t>2025-11-07T10:40:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T10:40:44+00:00</t>
+    <t>2025-11-25T08:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T08:22:04+00:00</t>
+    <t>2026-01-16T18:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Simple prescribed, dispensed, administered or used medication composed of one to many substances. If composed of many substance, the strengh SHALL be defined.</t>
+    <t>Simple prescribed, dispensed, administered or used medication composed of one to many substances. If composed of many substance, the strengh SHALL be defined. This ressource is profiled for describing a simple medication (vs compound medication) in the presription line represented by a MedicationRequest, a MedicationDispense or a MedicationUsage (pka MedicationStatement).
+Profil de la ressource Medication décrivant un médicament simple (vs médicament composé) dans la ligne de prescription, la dispensation ou l'administration représentée par une MedicationRequest, une MedicationDispense ou une MedicationStatement. Si le médicament est composé de plusieurs substances, la concentration de chaque substance doit être définie (ingredient.strength).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -271,7 +272,7 @@
     <t>Simple Medication</t>
   </si>
   <si>
-    <t>This ressource is profiled for describing a simple medication (vs compound medication) in the presription line represented by a MedicationRequest, a MedicationDispense or a MedicationUsage (pka MedicationStatement).</t>
+    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
   </si>
   <si>
     <t>A simple medication is made of one single component made of one to many substances.

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T18:04:25+00:00</t>
+    <t>2026-01-23T16:54:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T16:54:57+00:00</t>
+    <t>2026-01-23T16:56:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T16:56:48+00:00</t>
+    <t>2026-02-09T09:37:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T09:37:19+00:00</t>
+    <t>2026-02-23T11:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T11:15:05+00:00</t>
+    <t>2026-04-02T15:16:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:16:30+00:00</t>
+    <t>2026-05-04T12:24:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:24:40+00:00</t>
+    <t>2026-05-04T13:30:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:30:13+00:00</t>
+    <t>2026-05-06T13:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T13:16:54+00:00</t>
+    <t>2026-05-10T16:39:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-10T16:39:38+00:00</t>
+    <t>2026-05-10T16:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-10T16:47:08+00:00</t>
+    <t>2026-05-11T06:03:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T06:03:48+00:00</t>
+    <t>2026-05-11T06:11:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-noncompound.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T06:11:37+00:00</t>
+    <t>2026-07-10T14:23:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
